--- a/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/plan-financiero-parrillero-asador-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/plan-financiero-parrillero-asador-eventos.xlsx
@@ -6977,7 +6977,7 @@
       </c>
       <c r="E52" s="28" t="n"/>
     </row>
-    <row r="53" ht="45" customHeight="1">
+    <row r="53" ht="60" customHeight="1">
       <c r="A53" s="28" t="inlineStr">
         <is>
           <t>Pago de los ayuntamientos</t>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D53" s="46" t="inlineStr">
         <is>
-          <t>Contrato menor de servicios por debajo de 15.000 € (art. 118), sin anticipo, y factura electrónica por FACe si eres SL (Ley 25/2013, art. 4)</t>
+          <t>Contrato menor de servicios por debajo de 15.000 € (art. 118), sin anticipo, y factura electrónica por FACe si eres SL, salvo que exima las de hasta 5.000 € (Ley 25/2013, art. 4)</t>
         </is>
       </c>
       <c r="E53" s="28" t="n"/>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>Reglamento (CE) 853/2004 y RD 1086/2020, art. 30</t>
+          <t>Reglamento (CE) 853/2004 (recepción), AESAN (cocción, recomendación) y RD 1086/2020, art. 30 (mantenimiento)</t>
         </is>
       </c>
       <c r="D54" s="46" t="inlineStr">
@@ -7089,7 +7089,7 @@
     <row r="60">
       <c r="A60" s="79" t="inlineStr">
         <is>
-          <t>Versión 2.2 · septiembre 2026 · aichef.pro/plan-negocio-parrillero-asador-eventos · info@aichef.pro</t>
+          <t>Versión 2.2 · octubre 2026 · aichef.pro/plan-negocio-parrillero-asador-eventos · info@aichef.pro</t>
         </is>
       </c>
       <c r="B60" s="28" t="n"/>

--- a/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/plan-financiero-parrillero-asador-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/plan-financiero-parrillero-asador-eventos.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
         <v>0.022163583976983328</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de la furgoneta de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación, estanterías y anclajes), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de la furgoneta de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación, estanterías y anclajes), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así "&amp;"sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 8% de las partidas de la furgoneta de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación, estanterías y anclajes), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E28" s="28" t="n"/>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="25" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina de apoyo, Cuota de la cocina de apoyo de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina de apoyo, "&amp;"Cuota de la cocina de apoyo de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina de apoyo, Cuota de la cocina de apoyo de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman 33126 € de los 76522 € de inversión.</v>
       </c>
       <c r="E33" s="28" t="n"/>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>

--- a/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/plan-financiero-parrillero-asador-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/plan-financiero-parrillero-asador-eventos.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/plan-financiero-parrillero-asador-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/plan-financiero-parrillero-asador-eventos.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
         <v>0.022163583976983328</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de la furgoneta de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación, estanterías y anclajes), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de la furgoneta de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación, estanterías y anclajes), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así "&amp;"sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 8% de las partidas de la furgoneta de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación, estanterías y anclajes), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E28" s="28" t="n"/>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="25" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina de apoyo, Cuota de la cocina de apoyo de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina de apoyo, "&amp;"Cuota de la cocina de apoyo de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina de apoyo, Cuota de la cocina de apoyo de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman 33126 € de los 76522 € de inversión.</v>
       </c>
       <c r="E33" s="28" t="n"/>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>
